--- a/ProductCRMAPI/bin/Debug/Uploads/Invoice.xlsx
+++ b/ProductCRMAPI/bin/Debug/Uploads/Invoice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4B7411E-544B-4B71-9CF3-47F956E3C24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{728F0F28-7B3E-4EBB-B835-B38A7037614A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="56">
   <si>
     <t>SNO</t>
   </si>
@@ -57,6 +57,9 @@
     <t>Place Of Supply</t>
   </si>
   <si>
+    <t>InvoiceDate</t>
+  </si>
+  <si>
     <t>0001/26-27</t>
   </si>
   <si>
@@ -124,13 +127,87 @@
   </si>
   <si>
     <t>0008/26-27</t>
+  </si>
+  <si>
+    <t>0009/26-27</t>
+  </si>
+  <si>
+    <t>Pranjal</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>34xxxxxxx</t>
+  </si>
+  <si>
+    <t>Loha Bazar</t>
+  </si>
+  <si>
+    <t>0010/26-27</t>
+  </si>
+  <si>
+    <t>0011/26-27</t>
+  </si>
+  <si>
+    <t>8989898989</t>
+  </si>
+  <si>
+    <t>0012/26-27</t>
+  </si>
+  <si>
+    <t>Himanshu</t>
+  </si>
+  <si>
+    <t>787898989</t>
+  </si>
+  <si>
+    <t>45xxxxxxxxxx</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Rampur</t>
+  </si>
+  <si>
+    <t>0013/26-27</t>
+  </si>
+  <si>
+    <t>Ajay Rai</t>
+  </si>
+  <si>
+    <t>98765646456</t>
+  </si>
+  <si>
+    <t>23xxxxxxxxxxx</t>
+  </si>
+  <si>
+    <t>Banaras</t>
+  </si>
+  <si>
+    <t>0014/26-27</t>
+  </si>
+  <si>
+    <t>0015/26-27</t>
+  </si>
+  <si>
+    <t>0016/26-27</t>
+  </si>
+  <si>
+    <t>17/08/2026</t>
+  </si>
+  <si>
+    <t>0017/26-27</t>
+  </si>
+  <si>
+    <t>18/08/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -476,230 +553,463 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" bestFit="1" width="6" customWidth="1"/>
-    <col min="4" max="4" bestFit="1" width="7.85546875" customWidth="1"/>
-    <col min="5" max="5" bestFit="1" width="6.42578125" customWidth="1"/>
-    <col min="6" max="6" bestFit="1" width="5.7109375" customWidth="1"/>
-    <col min="7" max="7" bestFit="1" width="14.7109375" customWidth="1"/>
+    <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
         <v>7</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="B7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
         <v>8</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
         <v>9</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
         <v>10</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
         <v>11</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0">
-        <v>3</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
         <v>13</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
         <v>14</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
         <v>15</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
         <v>16</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17">
         <v>17</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="B17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0">
-        <v>4</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+      <c r="H18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
         <v>19</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0">
-        <v>5</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" s="0" t="s">
+      <c r="B19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F19" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0">
-        <v>6</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>7</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>8</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>9</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>24</v>
+      <c r="G19" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to Rahul under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>